--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_nuble_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_nuble_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:22</t>
+    <t xml:space="preserve">2026-09-29 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_nuble_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_nuble_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:13</t>
+    <t xml:space="preserve">2026-09-29 18:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -504,7 +504,7 @@
         <v>6.97</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>69.63</v>
+        <v>69.64</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>62.67</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_nuble_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_nuble_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:48</t>
+    <t xml:space="preserve">2026-10-05 04:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
